--- a/data/trans_orig/Q23-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/Q23-Provincia-trans_orig.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>15,8; 16,59</t>
+          <t>15,81; 16,62</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>15,96; 16,9</t>
+          <t>15,95; 16,94</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15,2; 16,5</t>
+          <t>15,27; 16,53</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16,26; 17,6</t>
+          <t>16,25; 17,56</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>16,89; 18,66</t>
+          <t>16,84; 18,62</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,03; 18,75</t>
+          <t>16,96; 18,56</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,08; 16,77</t>
+          <t>16,07; 16,79</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>16,48; 17,36</t>
+          <t>16,48; 17,33</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>16,15; 17,18</t>
+          <t>16,16; 17,22</t>
         </is>
       </c>
     </row>
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>15,82; 16,43</t>
+          <t>15,8; 16,41</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>15,82; 16,6</t>
+          <t>15,84; 16,61</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16,11; 16,78</t>
+          <t>16,06; 16,76</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16,96; 18,42</t>
+          <t>16,94; 18,51</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>16,76; 18,2</t>
+          <t>16,69; 18,16</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,79; 18,02</t>
+          <t>16,83; 17,98</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,28; 16,92</t>
+          <t>16,32; 16,96</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>16,31; 17,04</t>
+          <t>16,29; 17,02</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>16,45; 17,13</t>
+          <t>16,48; 17,07</t>
         </is>
       </c>
     </row>
@@ -897,7 +897,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15,66; 16,6</t>
+          <t>15,65; 16,56</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -907,37 +907,37 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16,56; 18,02</t>
+          <t>16,59; 18,04</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17,14; 19,45</t>
+          <t>17,07; 19,58</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>16,97; 18,54</t>
+          <t>16,93; 18,4</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16,9; 18,57</t>
+          <t>16,94; 18,67</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16,33; 17,39</t>
+          <t>16,3; 17,32</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>16,68; 17,47</t>
+          <t>16,68; 17,48</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16,83; 17,84</t>
+          <t>16,84; 17,9</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>16,15; 16,77</t>
+          <t>16,14; 16,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,98; 16,88</t>
+          <t>16,0; 16,89</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16,04; 17,26</t>
+          <t>16,06; 17,36</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17,18; 18,52</t>
+          <t>17,17; 18,42</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>18,22; 21,11</t>
+          <t>18,11; 21,07</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,37; 18,87</t>
+          <t>17,33; 18,81</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,64; 17,26</t>
+          <t>16,69; 17,34</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>16,98; 18,2</t>
+          <t>16,98; 18,18</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>16,73; 17,66</t>
+          <t>16,74; 17,65</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1117,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>16,36; 17,38</t>
+          <t>16,34; 17,35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15,94; 17,48</t>
+          <t>16,0; 17,67</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16,35; 17,59</t>
+          <t>16,34; 17,56</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16,33; 18,42</t>
+          <t>16,36; 18,4</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>16,43; 17,98</t>
+          <t>16,47; 17,89</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,19; 17,79</t>
+          <t>16,21; 17,73</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,52; 17,57</t>
+          <t>16,49; 17,54</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>16,34; 17,46</t>
+          <t>16,34; 17,45</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>16,41; 17,48</t>
+          <t>16,41; 17,41</t>
         </is>
       </c>
     </row>
@@ -1227,47 +1227,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>15,89; 16,82</t>
+          <t>15,9; 16,77</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>15,86; 17,08</t>
+          <t>15,89; 17,08</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>16,54; 18,22</t>
+          <t>16,55; 18,14</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>16,32; 17,61</t>
+          <t>16,37; 17,6</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>17,06; 19,48</t>
+          <t>17,07; 19,43</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>17,33; 19,52</t>
+          <t>17,31; 19,57</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>16,16; 16,89</t>
+          <t>16,13; 16,89</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>16,46; 17,62</t>
+          <t>16,46; 17,59</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>16,98; 18,2</t>
+          <t>16,98; 18,35</t>
         </is>
       </c>
     </row>
@@ -1337,47 +1337,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>16,02; 16,8</t>
+          <t>16,02; 16,76</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>16,19; 16,82</t>
+          <t>16,16; 16,77</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16,01; 16,68</t>
+          <t>16,02; 16,67</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17,42; 19,31</t>
+          <t>17,4; 19,14</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>16,91; 17,95</t>
+          <t>16,92; 17,95</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,76; 17,85</t>
+          <t>16,76; 17,88</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,66; 17,48</t>
+          <t>16,69; 17,56</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>16,53; 17,11</t>
+          <t>16,54; 17,09</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>16,43; 17,01</t>
+          <t>16,44; 17,02</t>
         </is>
       </c>
     </row>
@@ -1447,47 +1447,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>16,19; 17,01</t>
+          <t>16,16; 16,97</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>16,31; 16,84</t>
+          <t>16,32; 16,84</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16,01; 16,78</t>
+          <t>16,0; 16,8</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16,64; 17,51</t>
+          <t>16,7; 17,52</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>17,02; 18,26</t>
+          <t>17,0; 18,2</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,58; 19,03</t>
+          <t>17,57; 18,9</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,45; 17,04</t>
+          <t>16,44; 17,08</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>16,71; 17,32</t>
+          <t>16,7; 17,3</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>16,79; 17,58</t>
+          <t>16,8; 17,59</t>
         </is>
       </c>
     </row>
@@ -1557,47 +1557,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>16,19; 16,51</t>
+          <t>16,19; 16,5</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>16,32; 16,6</t>
+          <t>16,31; 16,61</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>16,31; 16,67</t>
+          <t>16,3; 16,66</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>17,21; 17,74</t>
+          <t>17,2; 17,75</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>17,41; 17,97</t>
+          <t>17,38; 17,95</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>17,39; 17,92</t>
+          <t>17,41; 17,92</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>16,64; 16,91</t>
+          <t>16,62; 16,89</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>16,77; 17,07</t>
+          <t>16,79; 17,06</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>16,83; 17,12</t>
+          <t>16,81; 17,13</t>
         </is>
       </c>
     </row>
